--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-produit-de-sante.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-produit-de-sante.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3684" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3684" uniqueCount="411">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -879,7 +879,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Autre codification - CIP : Code Identifiant de Présentation (1.2.250.1.213.2.3.2) de l'ANSM (13 chiffres) - UCD : Unités Communes de Dispensation (1.2.250.1.213.2.61) du Club Inter Pharmaceutique - ATC : Classification anatomique, thérapeutique et chimique (2.16.840.1.113883.6.73)  - MV : Médicament Virtuel (1.2.250.1.213.2.59) de Medicabase (MV+ 8 chiffres) </t>
+    <t>Autre codification - CIP : Code Identifiant de Présentation (1.2.250.1.213.2.3.2) de l'ANSM (13 chiffres) - UCD : Unités Communes de Dispensation (1.2.250.1.213.2.61) du Club Inter Pharmaceutique - ATC : Classification anatomique, thérapeutique et chimique (2.16.840.1.113883.6.73)  - MV : Médicament Virtuel (1.2.250.1.213.2.59) de Medicabase (MV+ 8 chiffres)</t>
   </si>
   <si>
     <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
@@ -965,7 +965,7 @@
     <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
+    <t xml:space="preserve">id
 </t>
   </si>
   <si>
@@ -976,6 +976,10 @@
   </si>
   <si>
     <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind.extension</t>
@@ -992,7 +996,7 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
@@ -1022,11 +1026,11 @@
     <t>Extensions that cannot be ignored even if unrecognized</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -9584,7 +9588,7 @@
         <v>76</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>75</v>
@@ -9595,14 +9599,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -9621,16 +9625,16 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9668,10 +9672,10 @@
         <v>75</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>75</v>
@@ -9680,7 +9684,7 @@
         <v>126</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -9692,7 +9696,7 @@
         <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>84</v>
@@ -9700,14 +9704,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -9726,19 +9730,19 @@
         <v>167</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>75</v>
@@ -9787,7 +9791,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -9799,18 +9803,18 @@
         <v>75</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9833,13 +9837,13 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9851,7 +9855,7 @@
         <v>75</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>75</v>
@@ -9890,7 +9894,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -9910,10 +9914,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9939,10 +9943,10 @@
         <v>301</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9993,7 +9997,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -10013,10 +10017,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10105,7 +10109,7 @@
         <v>76</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>75</v>
@@ -10116,14 +10120,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10142,16 +10146,16 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10189,10 +10193,10 @@
         <v>75</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>75</v>
@@ -10201,7 +10205,7 @@
         <v>126</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -10213,7 +10217,7 @@
         <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>84</v>
@@ -10221,14 +10225,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -10247,19 +10251,19 @@
         <v>167</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>75</v>
@@ -10308,7 +10312,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -10320,18 +10324,18 @@
         <v>75</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10354,13 +10358,13 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10411,7 +10415,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -10431,10 +10435,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10460,10 +10464,10 @@
         <v>193</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10514,7 +10518,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -10534,10 +10538,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10563,10 +10567,10 @@
         <v>284</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10617,7 +10621,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -10637,10 +10641,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10666,10 +10670,10 @@
         <v>301</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10720,7 +10724,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -10740,10 +10744,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10832,7 +10836,7 @@
         <v>76</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>75</v>
@@ -10843,14 +10847,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -10869,16 +10873,16 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -10916,10 +10920,10 @@
         <v>75</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>75</v>
@@ -10928,7 +10932,7 @@
         <v>126</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -10940,7 +10944,7 @@
         <v>75</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>84</v>
@@ -10948,14 +10952,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -10974,19 +10978,19 @@
         <v>167</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>75</v>
@@ -11035,7 +11039,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -11047,18 +11051,18 @@
         <v>75</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11081,13 +11085,13 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11099,7 +11103,7 @@
         <v>75</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>75</v>
@@ -11138,7 +11142,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -11158,10 +11162,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11184,13 +11188,13 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -11241,7 +11245,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -11261,10 +11265,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11290,10 +11294,10 @@
         <v>301</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11344,7 +11348,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -11364,10 +11368,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11456,7 +11460,7 @@
         <v>76</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>75</v>
@@ -11467,14 +11471,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -11493,16 +11497,16 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -11540,10 +11544,10 @@
         <v>75</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>75</v>
@@ -11552,7 +11556,7 @@
         <v>126</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -11564,7 +11568,7 @@
         <v>75</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>84</v>
@@ -11572,14 +11576,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -11598,19 +11602,19 @@
         <v>167</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>75</v>
@@ -11659,7 +11663,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -11671,18 +11675,18 @@
         <v>75</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11705,13 +11709,13 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11762,7 +11766,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -11782,10 +11786,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11808,13 +11812,13 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11865,7 +11869,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -11885,10 +11889,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11914,10 +11918,10 @@
         <v>193</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11968,7 +11972,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -11988,10 +11992,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12089,10 +12093,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12192,10 +12196,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12295,10 +12299,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12398,10 +12402,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12501,10 +12505,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12604,10 +12608,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12705,10 +12709,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12806,10 +12810,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12909,10 +12913,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12938,10 +12942,10 @@
         <v>264</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -12992,7 +12996,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -13012,10 +13016,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13115,10 +13119,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13218,10 +13222,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13247,10 +13251,10 @@
         <v>284</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13301,7 +13305,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -13321,10 +13325,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13347,7 +13351,7 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13400,7 +13404,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-produit-de-sante.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-produit-de-sante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1052,7 +1052,7 @@
     <t>Code indiquant qu'il s'agit d'une relation vers une classe générique ou thérapeutique.</t>
   </si>
   <si>
-    <t>GRIC</t>
+    <t>GRICAWATIF</t>
   </si>
   <si>
     <t>FRCDAMaterialPharm.asSpecializedKind.classCode</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-produit-de-sante.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-produit-de-sante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1052,7 +1052,7 @@
     <t>Code indiquant qu'il s'agit d'une relation vers une classe générique ou thérapeutique.</t>
   </si>
   <si>
-    <t>GRICAWATIF</t>
+    <t>GRIC</t>
   </si>
   <si>
     <t>FRCDAMaterialPharm.asSpecializedKind.classCode</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-produit-de-sante.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-produit-de-sante.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$142</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3684" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4560" uniqueCount="473">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -930,39 +930,40 @@
     <t>Material.sdtcExpirationTime</t>
   </si>
   <si>
-    <t>ManufacturedProduct.manufacturedMaterial.formCode</t>
-  </si>
-  <si>
-    <t>Forme pharmaceutique</t>
-  </si>
-  <si>
-    <t>Code représentant la forme pharmaceutique du produit de santé.</t>
-  </si>
-  <si>
-    <t>FRCDAMaterialPharm.formCode</t>
-  </si>
-  <si>
-    <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind</t>
+    <t>ManufacturedProduct.manufacturedMaterial.expirationTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVL_TS {http://hl7.org/cda/stds/core/StructureDefinition/IVL-TS|2.0.3-sd}
+</t>
+  </si>
+  <si>
+    <t>Date d'expiration du produit</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.expirationTime</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
 </t>
   </si>
   <si>
-    <t>Classification du produit</t>
-  </si>
-  <si>
-    <t>Relation entre le produit de santé et une classe générique ou thérapeutique.</t>
-  </si>
-  <si>
-    <t>FRCDAMaterialPharm.asSpecializedKind</t>
+    <t>Présentation / conditionnement</t>
+  </si>
+  <si>
+    <t>Description du conditionnement du produit de santé.</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind.id</t>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.id</t>
   </si>
   <si>
     <t xml:space="preserve">id
@@ -982,7 +983,7 @@
 </t>
   </si>
   <si>
-    <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind.extension</t>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.extension</t>
   </si>
   <si>
     <t>extensions
@@ -1016,7 +1017,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind.modifierExtension</t>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -1039,11 +1040,198 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind.classCode</t>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.classCode</t>
   </si>
   <si>
     <t xml:space="preserve">code
 </t>
+  </si>
+  <si>
+    <t>Classe de la relation contenu</t>
+  </si>
+  <si>
+    <t>CONT</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.classCode</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine</t>
+  </si>
+  <si>
+    <t>Conditionnement primaire</t>
+  </si>
+  <si>
+    <t>Description du conditionnement primaire du produit.</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.id</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.extension</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.modifierExtension</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.classCode</t>
+  </si>
+  <si>
+    <t>Classe du conditionnement</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.classCode</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.determinerCode</t>
+  </si>
+  <si>
+    <t>Type du conditionnement</t>
+  </si>
+  <si>
+    <t>INSTANCE</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.determinerCode</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.code</t>
+  </si>
+  <si>
+    <t>Code du produit de santé prescrit</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.code</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.name</t>
+  </si>
+  <si>
+    <t>Nom de marque du conditionnement</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.name</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.formCode</t>
+  </si>
+  <si>
+    <t>Conditionnement</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.formCode</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.capacityQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/PQ
+</t>
+  </si>
+  <si>
+    <t>Capacité du conditionnement primaire</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.capacityQuantity</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.asSuperContent</t>
+  </si>
+  <si>
+    <t>Conditionnement supérieur</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.asSuperContent.id</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.asSuperContent.extension</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.asSuperContent.modifierExtension</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.id</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.extension</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.modifierExtension</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.classCode</t>
+  </si>
+  <si>
+    <t>Classe du conditionnement supérieur</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.classCode</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.determinerCode</t>
+  </si>
+  <si>
+    <t>Type du conditionnement supérieur</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.determinerCode</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.capacityQuantity</t>
+  </si>
+  <si>
+    <t>Capacité du conditionnement supérieur</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.capacityQuantity</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.formCode</t>
+  </si>
+  <si>
+    <t>Forme pharmaceutique</t>
+  </si>
+  <si>
+    <t>Code représentant la forme pharmaceutique du produit de santé.</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.formCode</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind</t>
+  </si>
+  <si>
+    <t>Classification du produit</t>
+  </si>
+  <si>
+    <t>Relation entre le produit de santé et une classe générique ou thérapeutique.</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asSpecializedKind</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind.id</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind.extension</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind.modifierExtension</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind.classCode</t>
   </si>
   <si>
     <t>Classe de la relation</t>
@@ -1602,11 +1790,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK115"/>
+  <dimension ref="A1:AK142"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="86.05078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="86.05078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="117.390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="117.390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
@@ -1636,7 +1824,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="61.65625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="98.5" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -9201,7 +9389,7 @@
         <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>75</v>
@@ -9316,10 +9504,10 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>193</v>
+        <v>297</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>298</v>
@@ -9843,7 +10031,7 @@
         <v>331</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9855,46 +10043,46 @@
         <v>75</v>
       </c>
       <c r="S81" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -9914,10 +10102,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9943,10 +10131,10 @@
         <v>301</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9997,7 +10185,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -10017,10 +10205,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10120,10 +10308,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10225,10 +10413,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10332,10 +10520,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10361,10 +10549,10 @@
         <v>330</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10376,7 +10564,7 @@
         <v>75</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>185</v>
+        <v>332</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>75</v>
@@ -10415,7 +10603,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -10435,10 +10623,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10461,13 +10649,13 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>193</v>
+        <v>330</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10479,7 +10667,7 @@
         <v>75</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>75</v>
+        <v>346</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>75</v>
@@ -10518,7 +10706,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -10538,10 +10726,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10564,13 +10752,13 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>284</v>
+        <v>193</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10621,7 +10809,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -10641,10 +10829,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10655,7 +10843,7 @@
         <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>75</v>
@@ -10667,13 +10855,13 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10724,19 +10912,19 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>305</v>
+        <v>75</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>75</v>
@@ -10744,10 +10932,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10770,13 +10958,13 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>307</v>
+        <v>193</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>308</v>
+        <v>355</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10827,7 +11015,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -10836,32 +11024,32 @@
         <v>76</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>311</v>
+        <v>75</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>313</v>
+        <v>75</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>75</v>
@@ -10873,17 +11061,15 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>314</v>
+        <v>358</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>75</v>
@@ -10920,78 +11106,74 @@
         <v>75</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>318</v>
+        <v>75</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>319</v>
+        <v>75</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>321</v>
+        <v>75</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>323</v>
+        <v>75</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>167</v>
+        <v>75</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>167</v>
+        <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>75</v>
       </c>
@@ -11039,30 +11221,30 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>328</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11070,7 +11252,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>76</v>
@@ -11085,13 +11267,13 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>362</v>
+        <v>308</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11103,7 +11285,7 @@
         <v>75</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>364</v>
+        <v>75</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>75</v>
@@ -11142,41 +11324,41 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>365</v>
+        <v>310</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>75</v>
+        <v>313</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>75</v>
@@ -11188,15 +11370,17 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>367</v>
+        <v>314</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>368</v>
+        <v>315</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>75</v>
@@ -11233,74 +11417,78 @@
         <v>75</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>75</v>
+        <v>318</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>75</v>
+        <v>319</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>75</v>
+        <v>321</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>75</v>
+        <v>323</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>372</v>
+        <v>324</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
       </c>
@@ -11348,30 +11536,30 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>374</v>
+        <v>327</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>75</v>
+        <v>328</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11379,7 +11567,7 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>76</v>
@@ -11394,13 +11582,13 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>308</v>
+        <v>362</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>309</v>
+        <v>362</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11451,41 +11639,41 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>310</v>
+        <v>368</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>311</v>
+        <v>75</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>75</v>
+        <v>305</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>313</v>
+        <v>75</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>75</v>
@@ -11497,17 +11685,15 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>75</v>
@@ -11544,31 +11730,31 @@
         <v>75</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>318</v>
+        <v>75</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>319</v>
+        <v>75</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>321</v>
+        <v>75</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>84</v>
@@ -11576,14 +11762,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -11596,26 +11782,24 @@
         <v>75</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>167</v>
+        <v>75</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>167</v>
+        <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
         <v>314</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="O98" t="s" s="2">
-        <v>326</v>
-      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>75</v>
       </c>
@@ -11651,19 +11835,19 @@
         <v>75</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>75</v>
+        <v>318</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>75</v>
+        <v>319</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -11678,47 +11862,51 @@
         <v>321</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>328</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>75</v>
+        <v>323</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>379</v>
+        <v>324</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>75</v>
       </c>
@@ -11727,7 +11915,7 @@
         <v>75</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>75</v>
@@ -11766,30 +11954,30 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>381</v>
+        <v>327</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>75</v>
+        <v>321</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>75</v>
+        <v>328</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11815,10 +12003,10 @@
         <v>330</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11830,7 +12018,7 @@
         <v>75</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>189</v>
+        <v>332</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>75</v>
@@ -11869,7 +12057,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -11889,10 +12077,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11900,7 +12088,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>76</v>
@@ -11915,13 +12103,13 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>193</v>
+        <v>330</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11933,7 +12121,7 @@
         <v>75</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>75</v>
+        <v>346</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>75</v>
@@ -11972,10 +12160,10 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>76</v>
@@ -11992,20 +12180,18 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E102" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>76</v>
@@ -12020,11 +12206,13 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="L102" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="M102" t="s" s="2">
-        <v>88</v>
+        <v>379</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -12051,11 +12239,13 @@
         <v>75</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="Y102" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z102" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>75</v>
@@ -12073,10 +12263,10 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>91</v>
+        <v>380</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>76</v>
@@ -12093,18 +12283,16 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E103" t="s" s="2">
-        <v>63</v>
-      </c>
+      <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>81</v>
       </c>
@@ -12121,11 +12309,13 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="L103" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="M103" t="s" s="2">
-        <v>199</v>
+        <v>383</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12176,7 +12366,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>200</v>
+        <v>384</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -12196,18 +12386,16 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E104" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>81</v>
       </c>
@@ -12224,11 +12412,13 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L104" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="M104" t="s" s="2">
-        <v>203</v>
+        <v>387</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12279,7 +12469,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>204</v>
+        <v>388</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -12291,7 +12481,7 @@
         <v>75</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>75</v>
+        <v>305</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>75</v>
@@ -12299,18 +12489,16 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E105" t="s" s="2">
-        <v>206</v>
-      </c>
+      <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>81</v>
       </c>
@@ -12327,11 +12515,13 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L105" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="M105" t="s" s="2">
-        <v>207</v>
+        <v>309</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12382,7 +12572,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>208</v>
+        <v>310</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -12391,34 +12581,32 @@
         <v>76</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E106" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>75</v>
@@ -12430,13 +12618,17 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L106" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="M106" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>75</v>
@@ -12473,74 +12665,78 @@
         <v>75</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>75</v>
+        <v>318</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>75</v>
+        <v>319</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>212</v>
+        <v>320</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>75</v>
+        <v>321</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E107" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L107" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="M107" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>75</v>
       </c>
@@ -12588,30 +12784,30 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>216</v>
+        <v>327</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>75</v>
+        <v>321</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>75</v>
+        <v>328</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12619,7 +12815,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>76</v>
@@ -12634,11 +12830,13 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="L108" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="M108" t="s" s="2">
-        <v>219</v>
+        <v>394</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12650,7 +12848,7 @@
         <v>75</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>75</v>
+        <v>395</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>75</v>
@@ -12689,10 +12887,10 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>220</v>
+        <v>396</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>76</v>
@@ -12720,7 +12918,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>76</v>
@@ -12735,11 +12933,13 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L109" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="M109" t="s" s="2">
-        <v>222</v>
+        <v>399</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -12790,10 +12990,10 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>223</v>
+        <v>400</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>76</v>
@@ -12802,7 +13002,7 @@
         <v>75</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>75</v>
+        <v>305</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>75</v>
@@ -12810,18 +13010,16 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E110" t="s" s="2">
-        <v>225</v>
-      </c>
+      <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>81</v>
       </c>
@@ -12838,11 +13036,13 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="L110" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="M110" t="s" s="2">
-        <v>227</v>
+        <v>309</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -12893,7 +13093,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>228</v>
+        <v>310</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -12902,32 +13102,32 @@
         <v>76</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>75</v>
+        <v>313</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>75</v>
@@ -12939,15 +13139,17 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>264</v>
+        <v>314</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>400</v>
+        <v>315</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>75</v>
@@ -12984,34 +13186,34 @@
         <v>75</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>75</v>
+        <v>318</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>75</v>
+        <v>319</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>402</v>
+        <v>320</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>75</v>
+        <v>321</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="112" hidden="true">
@@ -13023,35 +13225,39 @@
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E112" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="L112" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="M112" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>75</v>
       </c>
@@ -13099,7 +13305,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>276</v>
+        <v>327</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -13111,10 +13317,10 @@
         <v>75</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>75</v>
+        <v>321</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>75</v>
+        <v>328</v>
       </c>
     </row>
     <row r="113" hidden="true">
@@ -13128,14 +13334,12 @@
       <c r="D113" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E113" t="s" s="2">
-        <v>278</v>
-      </c>
+      <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>75</v>
@@ -13147,11 +13351,13 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="L113" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="M113" t="s" s="2">
-        <v>281</v>
+        <v>406</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -13163,7 +13369,7 @@
         <v>75</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>75</v>
@@ -13202,13 +13408,13 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>282</v>
+        <v>407</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>75</v>
@@ -13222,10 +13428,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13248,13 +13454,13 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>284</v>
+        <v>193</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13305,7 +13511,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -13325,10 +13531,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13351,10 +13557,14 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="L115" s="2"/>
-      <c r="M115" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -13404,7 +13614,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -13419,11 +13629,2794 @@
         <v>75</v>
       </c>
       <c r="AK115" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E129" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="F129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L129" s="2"/>
+      <c r="M129" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="Y129" s="2"/>
+      <c r="Z129" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E130" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L130" s="2"/>
+      <c r="M130" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E131" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="F131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L131" s="2"/>
+      <c r="M131" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E132" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="F132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L132" s="2"/>
+      <c r="M132" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E133" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="F133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L133" s="2"/>
+      <c r="M133" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E134" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="F134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L134" s="2"/>
+      <c r="M134" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L135" s="2"/>
+      <c r="M135" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L136" s="2"/>
+      <c r="M136" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E137" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="F137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L137" s="2"/>
+      <c r="M137" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E139" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="F139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L139" s="2"/>
+      <c r="M139" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="140" hidden="true">
+      <c r="A140" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E140" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="F140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L140" s="2"/>
+      <c r="M140" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="141" hidden="true">
+      <c r="A141" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="142" hidden="true">
+      <c r="A142" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L142" s="2"/>
+      <c r="M142" s="2"/>
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
+      <c r="P142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK142" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK115">
+  <autoFilter ref="A1:AK142">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13433,7 +16426,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI114">
+  <conditionalFormatting sqref="A2:AI141">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
